--- a/docs/reports/20261020_回本側證據A段.xlsx
+++ b/docs/reports/20261020_回本側證據A段.xlsx
@@ -14,6 +14,7 @@
     <sheet name="3_推論支出口徑" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="4_牌價" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="5_世代上線" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="6_B段_推論支出" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="170">
   <si>
     <r>
       <rPr>
@@ -1080,7 +1081,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">。推論上兩者不可能同為「服務推論的完整直接成本」（無來源證實差額記在哪裡），至今沒有一手資料把 </t>
+      <t xml:space="preserve">。兩者口徑不同，不排除是同一件事、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億少算了記在其他科目的支出（差額去向無來源證實）；至今沒有一手資料把 </t>
     </r>
     <r>
       <rPr>
@@ -1166,6 +1186,25 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">Tokenomics </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">Microsoft </t>
     </r>
     <r>
@@ -1175,7 +1214,45 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">端帳單推估，可能含非現金 </t>
+      <t xml:space="preserve">端外洩文件前三季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">86.7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億外推的全年值（第四季＝第三季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 1.075</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），可能含研究推論與非現金 </t>
     </r>
     <r>
       <rPr>
@@ -1194,7 +1271,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">額度，</t>
+      <t xml:space="preserve">額度；</t>
     </r>
     <r>
       <rPr>
@@ -1213,7 +1290,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">發言人稱該數字「不太對」。</t>
+      <t xml:space="preserve">發言人對該外洩文件整體稱「不太對」。</t>
     </r>
   </si>
   <si>
@@ -2184,26 +2261,159 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">億主口徑（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Andy 2026-10-17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">「照建議」），並把 </t>
+      <t xml:space="preserve">億主口徑、區間 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75–88 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億不變（見 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6_B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段）。理由：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段查證最可能的解釋是部分服務算力（含免費用戶推論）記在營業成本以外——銷售費用中付 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft 5.27 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億，約占 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億差額的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">59%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tokenomics </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的服務機隊含免費用戶，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">84 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億的範圍較貼近。替代：主口徑改 </t>
     </r>
     <r>
       <rPr>
@@ -2222,7 +2432,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">億（查核財報）列為下一步要釐清的第一項：查 </t>
+      <t xml:space="preserve">億（唯一經查核、與營收同報表），</t>
     </r>
     <r>
       <rPr>
@@ -2241,26 +2451,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">億比 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">75 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億多出的部分是否記在研發。</t>
+      <t xml:space="preserve">億當高端敏感度；研究代理傾向此案。兩者判讀皆「未定」。</t>
     </r>
   </si>
   <si>
@@ -5394,7 +5585,64 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">推測多為訓練）；報導合計 </t>
+      <t xml:space="preserve">推測多為訓練）；銷售中付 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft 5.27 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億、管理 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.42 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億；四項合計 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">172.06 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億，與報導 </t>
     </r>
     <r>
       <rPr>
@@ -5413,45 +5661,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">億，但分項（含銷售 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.53</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、管理 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.04</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）加總 </t>
+      <t xml:space="preserve">億一致（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-21 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">更正：前版誤寫「加總 </t>
     </r>
     <r>
       <rPr>
@@ -5470,7 +5699,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">億，差約 </t>
+      <t xml:space="preserve">億、差 </t>
     </r>
     <r>
       <rPr>
@@ -5489,7 +5718,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">億，原因未明</t>
+      <t xml:space="preserve">億」）</t>
     </r>
   </si>
   <si>
@@ -5540,7 +5769,64 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">財報；定義「服務模型，主要是推論」；</t>
+      <t xml:space="preserve">財報（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2024 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">26.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億）。「服務模型，主要是推論」的定義在可讀轉述中未見原文，可能來自 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">或 </t>
     </r>
     <r>
       <rPr>
@@ -5559,26 +5845,45 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">取得、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FT 2026-06-16 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">核實（二手稿主要說核實淨虧損 </t>
+      <t xml:space="preserve">附註，無法確認。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zitron 2026-06-15 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">取得；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">核實（日期與範圍未查證；二手稿主要說核實淨虧損 </t>
     </r>
     <r>
       <rPr>
@@ -5597,7 +5902,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">億，其餘是否逐項核對未說明）</t>
+      <t xml:space="preserve">億）</t>
     </r>
   </si>
   <si>
@@ -5866,20 +6171,238 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Where's Your Ed At 2025-11-12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非公開數字：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tokenomics SRC_DEM_018 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的全年推估＝前三季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">86.7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Where's Your Ed At 2025-11-12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">外洩的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">端文件；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q1 20.75</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q2 29.47</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q3 36.48</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）＋第四季＝第三季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 1.075</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">39.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">125.9 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億；區間 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">123.2–128.6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">對應第四季持平至 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+15%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
     </r>
     <r>
       <rPr>
@@ -5898,45 +6421,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">推論類，含研究推論；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">前三季 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">86.7 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億＋第四季推估；可能含非現金 </t>
+      <t xml:space="preserve">推論類，可能含研究推論、可能含非現金 </t>
     </r>
     <r>
       <rPr>
@@ -5955,64 +6440,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">額度；不含 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CoreWeave</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Oracle</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Google </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">算力；</t>
+      <t xml:space="preserve">額度；供應商範圍未找到。</t>
     </r>
     <r>
       <rPr>
@@ -6031,7 +6459,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">發言人稱數字「不太對」</t>
+      <t xml:space="preserve">發言人對整份外洩文件稱「不太對」</t>
     </r>
   </si>
   <si>
@@ -6074,7 +6502,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">億：兩者不可能同為服務推論的完整直接成本。可能解釋（無來源證實）：差額記在研發；或 </t>
+      <t xml:space="preserve">億：兩者口徑不同，不排除實質是同一件事、只是 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億少算了某些支出（記在其他科目）。可能解釋（無來源證實）：差額記在研發；或 </t>
     </r>
     <r>
       <rPr>
@@ -8034,6 +8481,2173 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">逐世代 可試算）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段查證（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-21</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；研究代理，所有頁面皆二手轉述，</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FT</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">The Information </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原文未讀到）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">三個數字不是同一件事的三個估計</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">審計後營業成本（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2024 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">26.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億）。付 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft 60.47 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80.6%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），其餘約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億未揭露。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zitron 2026-06-15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TechTimes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Fortune</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TechSpot </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述同一文件（不獨立）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">核實的範圍無法確認</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">84 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">管理層投資人資料的「推論」（免費約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">39 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億＋付費約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">45 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">預期 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">141 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">The Information 2026-02-25 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">經二手摘要；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">The Decoder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Sacra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">疑同源。供應商範圍、研究推論、現金或應計口徑皆找不到。同一資料的調整後毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">33% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">換算約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">88 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億（＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tokenomics </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">高端 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">126 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">沒有公開出處：是 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tokenomics </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">由 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">端前三季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">86.7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億外推的全年值（第四季＝第三季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 1.075</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">端前三季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">86.7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億已高於付 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的營業成本 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">60.47 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億，也高於 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">84 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上半年營業成本超過 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億，約為同期 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">端推論 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億的一半——研究代理推測 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">端範圍較大（推測）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">保留</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">84 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億與同一資料的調整後毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">33% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">對不上：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(13.07−8.4)÷13.07</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">35.7%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、用 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">42.6%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，皆非 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">33%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，所以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">84 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不能互相印證。另外 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2024 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年推論約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億小於營業成本 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">26.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年卻是 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">84 &gt; 75</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，方向反轉，研究代理標為值得警惕</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">84 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">比 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">多出 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">最可能（證據偏弱）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分服務算力（免費用戶、評測或研究推論）記在營業成本以外的研發或銷售費用。銷售費用 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年增 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">418% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">至 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">57.3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億，其中付 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft 5.27 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億，約占差額 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">59%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；研發中付 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft 105.9 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億（多為訓練，推測）也可能含一部分。沒有來源明說</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">其次（弱）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">應計與現金、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Azure </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">額度抵減、非 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">供應商的口徑差異；或管理層「調整後」口徑含非 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GAAP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">調整</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">對齊分析</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">找不到任何來源把 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">84</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">126 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">明確對齊</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">chat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">端判斷</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tokenomics </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的所需 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">是「服務機隊（含免費用戶）的持有成本 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收」。若「免費用戶推論記在銷售費用」的解釋成立，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億低估了服務機隊成本，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">84 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億的範圍較貼近模型定義；反之若 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">84 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億含研究推論，則高估。兩種方向都有可能，所以維持 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">84 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億為基準、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75–88 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億為區間，並把比值寫成區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">84 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">88 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.96</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），不寫「剛好回本」。研究代理建議改以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億為主口徑（唯一經查核），列為替代方案</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上半年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">57 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億、毛利率約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">39%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、營業損失 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">93 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GAAP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">口徑；未審計，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">The Decoder </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zitron </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">另報非 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GAAP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業利益率 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">122%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，口徑不同不可混用）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">67 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WSJ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">經轉述）；營業成本或推論金額找不到</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">下一步（可選）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">取得查核財報附註（營業成本組成、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Azure </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">額度、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">對價處理）或 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zitron </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">付費段落；這是縮小 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">84 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">差距唯一的直接途徑，需付費來源（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">線下調研項）</t>
     </r>
   </si>
 </sst>
@@ -8533,7 +11147,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
@@ -8566,7 +11180,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
         <v>11</v>
       </c>
@@ -9573,7 +12187,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>87</v>
       </c>
@@ -9584,7 +12198,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
@@ -9617,14 +12231,14 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>96</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>12.6</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -9888,4 +12502,122 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="100"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>